--- a/data/daily/2026-10/2026-10-28.xlsx
+++ b/data/daily/2026-10/2026-10-28.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="카카오선물하기" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="올리브영" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="올리브영_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1394,261 +1392,6 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2088,18 +1831,18 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함</t>
+          <t>고급스러운 패키지 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 피로가 쌓였을 때 섭취 시 컨디션 유지 및 활력 보충에 도움됨</t>
+          <t>체력 및 피로 개선 — 피로가 쌓이고 체력이 떨어졌을 때 복용 시 활력에 도움을 줌</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>쇼핑백 옵션 부재 아쉬움 — 직접 전달 시 필요한 쇼핑백 구성이나 선택 옵션이 없음</t>
+          <t>쇼핑백 미제공 아쉬움 — 직접 전달 시 필요한 쇼핑백이 구성에 포함되어 있지 않음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2143,16 +1886,16 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15698</v>
+        <v>15700</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>깔끔하고 세련된 패키지 — 뽁뽁이로 안전하게 배송되며 심플하고 세련된 디자인을 갖춤</t>
+          <t>피로 회복 및 건강 증진 — 감기 예방 및 피로 해소에 도움을 주어 하루 충전에 효과적임</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 섭취와 하루 충전 — 부담 없이 간편하게 섭취하며 비타민과 미네랄을 한 번에 챙김</t>
+          <t>깔끔한 패키지 디자인 — 위생적이고 세련된 디자인으로 식탁이나 책상에 두고 먹기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -2202,19 +1945,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 지칠 때 먹으면 에너지가 올라가고 피로 회복에 효과적임</t>
+          <t>확실한 피로 회복 및 활력 — 체력이 떨어지거나 지칠 때 섭취 시 활력 충전 효과가 확실함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>농도 짙은 고품질 액상 — 타 제품 대비 액상 비타민 농도가 짙고 고품질 느낌을 줌</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>넉넉한 용량으로 대가족용 — 30입 구성으로 양이 넉넉하여 온 가족이 나눠 먹기 좋음</t>
-        </is>
-      </c>
+          <t>넉넉한 용량과 진한 농도 — 액상 비타민 농도가 진하고 양이 넉넉하여 가족과 나누어 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2261,25 +2000,21 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>젤리 형태의 간편한 섭취 — 물 없이 씹어 먹는 구미 타입으로 챙겨 먹기 편리함</t>
+          <t>맛있고 간편한 구미 제형 — 물 없이도 간식처럼 씹어 먹을 수 있는 새콤달콤한 젤리 형태임</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>적당한 단맛과 쫄깃함 — 과하게 달지 않고 적당히 말랑하며 쫄깃한 식감을 가짐</t>
+          <t>부담 없는 달콤함과 식감 — 과하게 달지 않고 쫄깃하여 남녀노소 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>포장 개봉의 극심한 불편 — 밀봉 포장이 잘 뜯어지지 않아 개봉 시 불편함을 겪음</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>어린이 비타민 같은 맛 — 성인용 영양제보다 어린이 비타민이나 간식 젤리 느낌이 듦</t>
-        </is>
-      </c>
+          <t>개봉하기 어려운 포장 — 입구 포장이 잘 뜯기지 않아 개봉 시 불편함이 발생함</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2324,12 +2059,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 환절기 피로 회복에 좋고 몸과 마음을 상쾌하게 해줌</t>
+          <t>우수한 피로 회복 효과 — 환절기 및 바쁜 일상 속 피로 해소에 큰 도움을 줌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 섭취 편의 — 개별 포장으로 복용이 간편하고 휴대하기 용이함</t>
+          <t>편리한 휴대성 및 섭취 — 휴대와 복용이 간편하여 평소에 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2340,7 +2075,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2348,43 +2083,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8768</v>
+        <v>1813</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠르고 정확한 배송 — 배송이 신속하게 이루어져 빠르게 수령할 수 있음</t>
+          <t>간편한 휴대 및 음용 방법 — 가방에 하나씩 넣어 다니며 피곤할 때 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 활력 충전 — 피곤한 아침에 간편하게 먹어 활력을 얻기에 적합함</t>
+          <t>고급 포장과 상큼한 맛 — 포장이 매우 고급스럽고 맛이 상큼하여 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2395,7 +2130,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2403,50 +2138,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1813</v>
+        <v>8768</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 가방 속 휴대성 — 가방에 하나씩 챙겨 다니며 피곤할 때 먹기 좋게 구성됨</t>
+          <t>신속한 배송 서비스 — 배송이 빠르고 안전하게 도착하여 이용에 만족스러움</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 증정 — 포장이 깔끔하고 고급스러우며 1입 추가 증정이 제공됨</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 체력 보충 — 맛이 상큼하고 체력 보충 및 비타민 충전에 효과적임</t>
-        </is>
-      </c>
+          <t>피로 회복 및 활력 충전 — 아침이나 피곤한 날 복용 시 활력을 되찾는 데 효과적임</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2493,23 +2224,23 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>휴대성 높은 멀티팩 포장 — 포 형태로 개별 포장되어 외출이나 여행 시 지참하기 편리함</t>
+          <t>개별 포장의 뛰어난 휴대성 — 컴팩트한 포 형태로 외출이나 여행 시 지니고 다니기 편리함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>꾸준한 섭취로 활력 증진 — 꾸준히 복용 시 활력이 생기고 피로 극복에 도움이 됨</t>
+          <t>체력 증진 및 활력 개선 — 꾸준히 복용 시 에너지가 생기고 힘이 나는 것을 체감함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>배송 중 박스 구겨짐 — 배송 과정에서 제품 상자가 구겨져서 도착함</t>
+          <t>배송 중 박스 구겨짐 — 배송 과정에서 포장 박스가 구겨져 배송 상태에 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>사은품 품질의 아쉬움 — 동봉된 사은품이 저가 매장 상품으로 구성되어 아쉬움</t>
+          <t>사은품 품질 아쉬움 — 제공된 사은품의 품질 만족도가 다소 떨어짐</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2556,18 +2287,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 바쁘고 피곤할 때 먹으면 활력이 도는 뛰어난 효과를 보임</t>
+          <t>빠른 배송 및 편한 섭취 — 배송 상태가 양호하며 복용 방법이 간편함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리한 복용과 빠른 배송 — 배송 상태가 좋고 복용 방법이 편리하여 만족함</t>
+          <t>바쁜 일상 속 활력 개선 — 바쁘고 힘들 때 미리 챙겨 먹으면 활력 증진에 도움을 줌</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약과 비슷한 느낌이라 맛에 호불호가 있음</t>
+          <t>약 맛 느낌의 호불호 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2604,7 +2335,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261028140647_0fd4e06070a142d99b2be50613487713.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -2615,12 +2346,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성분 대비 뛰어난 가성비 — 타 브랜드 비타민 대비 성분과 가격 면에서 실속이 뛰어남</t>
+          <t>성분 대비 뛰어난 가성비 — 타사 유명 제품 대비 성분이 알차고 가격이 실속 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>아침 상쾌함과 컨디션 회복 — 피곤한 아침 섭취 시 커피 없이도 상쾌하고 컨디션 회복에 도움됨</t>
+          <t>피로 회복 및 컨디션 개선 — 피곤한 아침이나 컨디션 난조 시 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -2639,60 +2370,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로차진액 스틱 5포 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026141404_b1c5e3127aad4b51b5e3d0ac9e906be1.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>978</v>
+        <v>119</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>더부룩함 완화와 소화 개선 — 섭취 후 속 더부룩함이 사라지고 배변 활동에 도움이 됨</t>
+          <t>뛰어난 숙취 해소 효과 — 음주 전후 상관없이 섭취 가능하며 다음 날 숙취 부담을 줄여줌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>고소하고 달콤한 풍미 — 초당옥수수 등 달콤하고 고소한 맛으로 먹기 부담 없음</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>풍성한 증정 사은품 — 견과류 바 등 알찬 증정품이 함께 제공됨</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>과한 단맛에 대한 아쉬움 — 단맛이 다소 강하여 조금 덜 달았으면 하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>이전 대비 줄어든 용량 — 기존 제품에 비해 2g 용량으로 양이 적게 느껴짐</t>
-        </is>
-      </c>
+          <t>휴대하기 좋은 개별 포장 — 개별 포장 및 깔끔한 세트 구성으로 가방에 챙겨 다니기 용이함</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13" ht="38" customHeight="1">
@@ -2706,58 +2425,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로차진액 스틱 5포 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026141404_b1c5e3127aad4b51b5e3d0ac9e906be1.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>119</v>
+        <v>981</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 속이 편안하고 빠른 회복에 도움됨</t>
+          <t>소화 개선 및 더부룩함 완화 — 음식 섭취 후 더부룩한 느낌을 줄여주고 소화를 도움</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>낱개 포장의 우수한 휴대성 — 1포씩 개별 포장되어 가방에 들고 다니기 유용함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>선물용으로 적합한 패키지 — 포장이 깔끔하게 잘 되어 있어 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>고소한 맛과 푸짐한 증정품 — 달콤 고소한 맛과 함께 다양한 추가 사은품이 증정됨</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>과한 단맛과 변경된 용량 — 단맛이 세게 느껴질 수 있으며 기존 대비 용량과 맛에 변화가 있음</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2765,47 +2484,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>112,200원</t>
+          <t>44,500원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12201735</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261022235449_5267b277d2d34792874c370e57c948d8.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026140618_d8294b0175c344218da6d62160aa60a0.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>35</v>
+        <v>1769</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 36가지의 다양한 종류가 있어 질리지 않고 지속 식단 가능함</t>
+          <t>속 편한 소화 촉진 효과 — 밀가루나 소화가 안 되는 음식을 먹었을 때 속을 편하게 해줌</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 살코기가 퍽퍽하지 않고 부드럽고 촉촉함</t>
+          <t>텁텁하지 않은 고소한 맛 — 미숫가루처럼 고소하고 텁텁함이 없어 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>기프티콘 안내 부족 — 이벤트 기프티콘 확인 방법에 대한 설명이 불명확함</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -2820,7 +2543,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2830,44 +2553,48 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44,500원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026140618_d8294b0175c344218da6d62160aa60a0.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1769</v>
+        <v>286</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편안함 — 과식이나 밀가루 섭취 후 먹으면 소화가 잘되고 속이 편함</t>
+          <t>다양하고 맛있는 맛 종류 — 크림소다, 카카오 등 여러 가지 맛이 있어 취향껏 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루 같은 고소한 맛이 남</t>
+          <t>만족스러운 콜라보 구성품 — 포토카드 및 단백질바 포함으로 상품 구성의 만족도가 높음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>포토카드 누락 및 구겨짐 — 배송 시 포토카드가 구겨져 올 위험이 있어 포장 주의가 요구됨</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2875,54 +2602,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026100840_629c26bcd34b4b2c9b2b3dbda7297fd4.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>284</v>
+        <v>763</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>맛있는 다양한 풍미 — 크림소다, 쿠키앤크림 등 다양한 맛이 있어 맛있게 먹음</t>
+          <t>고급스러운 오간자 포장 — 패키지와 오간자 포장이 아름다워 선물 시 만족도가 뛰어남</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>포토카드 및 단백질바 증정 — 포토카드와 단백질바 등 알찬 사은품으로 구성됨</t>
+          <t>맛있는 섭취감과 음용 편의 — 비린 맛 없이 맛이 좋아 하루 한 병 간편하게 마시기 양호함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>오간자 포장 누락 배송 — 안내와 달리 오간자 포장이 빠진 상태로 배송되는 경우 발생함</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2930,51 +2661,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>허닭</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/1115219</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026100840_629c26bcd34b4b2c9b2b3dbda7297fd4.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>763</v>
+        <v>1931</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 오간자 및 플리츠백 구성으로 고급스러워 선물 시 감동을 줌</t>
+          <t>질리지 않는 다양한 구성 — 20종의 다양한 구성으로 식단 관리 중 질리지 않고 섭취 가능함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>맛있고 편리한 섭취 — 앰플 형태라 챙겨 먹기 쉽고 맛도 좋음</t>
+          <t>증정 용기 이용 간편 조리 — 전자레인지 전용 용기가 함께 증정되어 조리가 편리함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>오간자 포장 누락 배송 — 선물용 오간자 포장이 누락되어 배송되는 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3020,12 +2747,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 간단한 조리 — 닭가슴살이 촉촉하며 전자레인지로 데워 먹기 편리함</t>
+          <t>촉촉한 식감과 맛있는 양념 — 퍽퍽하지 않고 촉촉하며 떡볶이 맛 등 양념 맛이 우수함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 양념 — 떡볶이맛 등 맛있는 양념이 어우러져 질리지 않음</t>
+          <t>전자레인지 간편 조리 — 전자레인지에 데워 바로 먹을 수 있어 식사 대용으로 간편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -3044,51 +2771,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>허닭</t>
+          <t>가농</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/1115219</t>
+          <t>https://gift.kakao.com/product/14380726</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1931</v>
+        <v>35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>다채로운 상품 구성 — 닭가슴살 외에도 다양한 상품이 포함되어 질리지 않음</t>
+          <t>껍질 안 까는 흰자 간편식 — 계란 껍질을 깔 필요 없이 흰자만 깔끔하게 단백질 보충 가능함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>전용 렌지 용기 증정 — 전자레인지용 전용 용기가 함께 제공되어 간편히 데움</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>부드럽고 촉촉한 질감 — 퍽퍽함 없이 촉촉하여 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>비리지 않고 적절한 간 — 비린 맛이 없고 적당히 짭짤하여 부담 없이 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>단일 맛 구성과 박스 상태 — 혼합 맛 구성 옵션이 없으며 배송 박스 위생 상태가 아쉬움</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3103,55 +2830,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>가농</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14380726</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>계란 흰자만 간편 섭취 — 삶거나 껍질을 깔 필요 없이 흰자만 바로 먹기 유용함</t>
+          <t>비린 맛 없는 음료 같은 맛 — 단백질 음료 특유의 비린 맛이나 느끼함 없이 음료처럼 마시기 좋음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>비린 맛없는 적당한 간 — 비린내가 나지 않고 적당히 짭짤하여 아침 대용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>노른자 없이 낮은 칼로리 — 노른자가 빠져 퍽퍽하지 않고 칼로리 부담 없이 단백질 채움</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>배송 박스 상태 아쉬움 — 제품은 양호하나 배송용 박스가 깨끗하지 않고 재활용 느낌이 남</t>
-        </is>
-      </c>
+          <t>운동 후 간편 단백질 보충 — 운동 후 챙겨 먹기 편하며 배고픔을 달래주는 포만감이 있음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3166,43 +2885,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
+          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>112,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/12201735</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261022235449_5267b277d2d34792874c370e57c948d8.png</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>비린 맛없는 맛있는 풍미 — 프로틴 특유의 비린 맛이 없고 음료처럼 달콤하고 맛있음</t>
+          <t>부드러운 육질과 다양성 — 닭가슴살 육질이 부드럽고 다채로운 맛이 포함되어 만족스러움</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>운동 후 든든한 포만감 — 운동 후 섭취 시 배고픔이 줄고 포만감이 오래 유지됨</t>
+          <t>다이어트 간편 식단 — 조리가 간편하여 지속적인 다이어트 체중 관리 식단으로 이용하기 좋음</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -3346,12 +3065,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3403,12 +3122,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>뉴트리포유</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3460,12 +3179,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3531,7 +3250,7 @@
         <v>16361</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15698</v>
+        <v>15700</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3427</v>
@@ -3543,10 +3262,10 @@
         <v>834</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>8768</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>1813</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>103</v>
@@ -3558,7 +3277,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -3566,64 +3285,62 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함
-피로 회복 및 활력 증진 — 피로가 쌓였을 때 섭취 시 컨디션 유지 및 활력 보충에 도움됨</t>
+          <t>고급스러운 패키지 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함
+체력 및 피로 개선 — 피로가 쌓이고 체력이 떨어졌을 때 복용 시 활력에 도움을 줌</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>깔끔하고 세련된 패키지 — 뽁뽁이로 안전하게 배송되며 심플하고 세련된 디자인을 갖춤
-간편한 섭취와 하루 충전 — 부담 없이 간편하게 섭취하며 비타민과 미네랄을 한 번에 챙김</t>
+          <t>피로 회복 및 건강 증진 — 감기 예방 및 피로 해소에 도움을 주어 하루 충전에 효과적임
+깔끔한 패키지 디자인 — 위생적이고 세련된 디자인으로 식탁이나 책상에 두고 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 지칠 때 먹으면 에너지가 올라가고 피로 회복에 효과적임
-농도 짙은 고품질 액상 — 타 제품 대비 액상 비타민 농도가 짙고 고품질 느낌을 줌
-넉넉한 용량으로 대가족용 — 30입 구성으로 양이 넉넉하여 온 가족이 나눠 먹기 좋음</t>
+          <t>확실한 피로 회복 및 활력 — 체력이 떨어지거나 지칠 때 섭취 시 활력 충전 효과가 확실함
+넉넉한 용량과 진한 농도 — 액상 비타민 농도가 진하고 양이 넉넉하여 가족과 나누어 먹기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>젤리 형태의 간편한 섭취 — 물 없이 씹어 먹는 구미 타입으로 챙겨 먹기 편리함
-적당한 단맛과 쫄깃함 — 과하게 달지 않고 적당히 말랑하며 쫄깃한 식감을 가짐</t>
+          <t>맛있고 간편한 구미 제형 — 물 없이도 간식처럼 씹어 먹을 수 있는 새콤달콤한 젤리 형태임
+부담 없는 달콤함과 식감 — 과하게 달지 않고 쫄깃하여 남녀노소 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 환절기 피로 회복에 좋고 몸과 마음을 상쾌하게 해줌
-우수한 휴대성과 섭취 편의 — 개별 포장으로 복용이 간편하고 휴대하기 용이함</t>
+          <t>우수한 피로 회복 효과 — 환절기 및 바쁜 일상 속 피로 해소에 큰 도움을 줌
+편리한 휴대성 및 섭취 — 휴대와 복용이 간편하여 평소에 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠르고 정확한 배송 — 배송이 신속하게 이루어져 빠르게 수령할 수 있음
-간편한 활력 충전 — 피곤한 아침에 간편하게 먹어 활력을 얻기에 적합함</t>
+          <t>간편한 휴대 및 음용 방법 — 가방에 하나씩 넣어 다니며 피곤할 때 간편하게 섭취 가능함
+고급 포장과 상큼한 맛 — 포장이 매우 고급스럽고 맛이 상큼하여 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가방 속 휴대성 — 가방에 하나씩 챙겨 다니며 피곤할 때 먹기 좋게 구성됨
-고급스러운 포장과 증정 — 포장이 깔끔하고 고급스러우며 1입 추가 증정이 제공됨
-상큼한 맛과 체력 보충 — 맛이 상큼하고 체력 보충 및 비타민 충전에 효과적임</t>
+          <t>신속한 배송 서비스 — 배송이 빠르고 안전하게 도착하여 이용에 만족스러움
+피로 회복 및 활력 충전 — 아침이나 피곤한 날 복용 시 활력을 되찾는 데 효과적임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>휴대성 높은 멀티팩 포장 — 포 형태로 개별 포장되어 외출이나 여행 시 지참하기 편리함
-꾸준한 섭취로 활력 증진 — 꾸준히 복용 시 활력이 생기고 피로 극복에 도움이 됨</t>
+          <t>개별 포장의 뛰어난 휴대성 — 컴팩트한 포 형태로 외출이나 여행 시 지니고 다니기 편리함
+체력 증진 및 활력 개선 — 꾸준히 복용 시 에너지가 생기고 힘이 나는 것을 체감함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 바쁘고 피곤할 때 먹으면 활력이 도는 뛰어난 효과를 보임
-편리한 복용과 빠른 배송 — 배송 상태가 좋고 복용 방법이 편리하여 만족함</t>
+          <t>빠른 배송 및 편한 섭취 — 배송 상태가 양호하며 복용 방법이 간편함
+바쁜 일상 속 활력 개선 — 바쁘고 힘들 때 미리 챙겨 먹으면 활력 증진에 도움을 줌</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성분 대비 뛰어난 가성비 — 타 브랜드 비타민 대비 성분과 가격 면에서 실속이 뛰어남
-아침 상쾌함과 컨디션 회복 — 피곤한 아침 섭취 시 커피 없이도 상쾌하고 컨디션 회복에 도움됨</t>
+          <t>성분 대비 뛰어난 가성비 — 타사 유명 제품 대비 성분이 알차고 가격이 실속 있음
+피로 회복 및 컨디션 개선 — 피곤한 아침이나 컨디션 난조 시 회복에 도움을 줌</t>
         </is>
       </c>
     </row>
@@ -3635,15 +3352,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 옵션 부재 아쉬움 — 직접 전달 시 필요한 쇼핑백 구성이나 선택 옵션이 없음</t>
+          <t>쇼핑백 미제공 아쉬움 — 직접 전달 시 필요한 쇼핑백이 구성에 포함되어 있지 않음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 극심한 불편 — 밀봉 포장이 잘 뜯어지지 않아 개봉 시 불편함을 겪음
-어린이 비타민 같은 맛 — 성인용 영양제보다 어린이 비타민이나 간식 젤리 느낌이 듦</t>
+          <t>개봉하기 어려운 포장 — 입구 포장이 잘 뜯기지 않아 개봉 시 불편함이 발생함</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3651,13 +3367,13 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 박스 구겨짐 — 배송 과정에서 제품 상자가 구겨져서 도착함
-사은품 품질의 아쉬움 — 동봉된 사은품이 저가 매장 상품으로 구성되어 아쉬움</t>
+          <t>배송 중 박스 구겨짐 — 배송 과정에서 포장 박스가 구겨져 배송 상태에 아쉬움이 남음
+사은품 품질 아쉬움 — 제공된 사은품의 품질 만족도가 다소 떨어짐</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 약 맛 — 오렌지 맛 감기약과 비슷한 느낌이라 맛에 호불호가 있음</t>
+          <t>약 맛 느낌의 호불호 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -3695,12 +3411,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>19,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -3868,22 +3584,22 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3915,52 +3631,52 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>허닭</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>가농</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>허닭</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>가농</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
         </is>
       </c>
     </row>
@@ -3972,52 +3688,52 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로차진액 스틱 5포 증정</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나</t>
         </is>
       </c>
     </row>
@@ -4065,37 +3781,37 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>978</v>
+        <v>119</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>119</v>
+        <v>981</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35</v>
+        <v>1769</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1769</v>
+        <v>286</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>284</v>
+        <v>763</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>763</v>
+        <v>1931</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>73</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1931</v>
+        <v>35</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4103,97 +3819,100 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 완화와 소화 개선 — 섭취 후 속 더부룩함이 사라지고 배변 활동에 도움이 됨
-고소하고 달콤한 풍미 — 초당옥수수 등 달콤하고 고소한 맛으로 먹기 부담 없음
-풍성한 증정 사은품 — 견과류 바 등 알찬 증정품이 함께 제공됨</t>
+          <t>뛰어난 숙취 해소 효과 — 음주 전후 상관없이 섭취 가능하며 다음 날 숙취 부담을 줄여줌
+휴대하기 좋은 개별 포장 — 개별 포장 및 깔끔한 세트 구성으로 가방에 챙겨 다니기 용이함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 속이 편안하고 빠른 회복에 도움됨
-낱개 포장의 우수한 휴대성 — 1포씩 개별 포장되어 가방에 들고 다니기 유용함
-선물용으로 적합한 패키지 — 포장이 깔끔하게 잘 되어 있어 지인 선물용으로 적합함</t>
+          <t>소화 개선 및 더부룩함 완화 — 음식 섭취 후 더부룩한 느낌을 줄여주고 소화를 도움
+고소한 맛과 푸짐한 증정품 — 달콤 고소한 맛과 함께 다양한 추가 사은품이 증정됨</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 36가지의 다양한 종류가 있어 질리지 않고 지속 식단 가능함
-부드럽고 촉촉한 식감 — 살코기가 퍽퍽하지 않고 부드럽고 촉촉함</t>
+          <t>속 편한 소화 촉진 효과 — 밀가루나 소화가 안 되는 음식을 먹었을 때 속을 편하게 해줌
+텁텁하지 않은 고소한 맛 — 미숫가루처럼 고소하고 텁텁함이 없어 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편안함 — 과식이나 밀가루 섭취 후 먹으면 소화가 잘되고 속이 편함
-고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루 같은 고소한 맛이 남</t>
+          <t>다양하고 맛있는 맛 종류 — 크림소다, 카카오 등 여러 가지 맛이 있어 취향껏 맛있게 먹기 좋음
+만족스러운 콜라보 구성품 — 포토카드 및 단백질바 포함으로 상품 구성의 만족도가 높음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 다양한 풍미 — 크림소다, 쿠키앤크림 등 다양한 맛이 있어 맛있게 먹음
-포토카드 및 단백질바 증정 — 포토카드와 단백질바 등 알찬 사은품으로 구성됨</t>
+          <t>고급스러운 오간자 포장 — 패키지와 오간자 포장이 아름다워 선물 시 만족도가 뛰어남
+맛있는 섭취감과 음용 편의 — 비린 맛 없이 맛이 좋아 하루 한 병 간편하게 마시기 양호함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 오간자 및 플리츠백 구성으로 고급스러워 선물 시 감동을 줌
-맛있고 편리한 섭취 — 앰플 형태라 챙겨 먹기 쉽고 맛도 좋음</t>
+          <t>질리지 않는 다양한 구성 — 20종의 다양한 구성으로 식단 관리 중 질리지 않고 섭취 가능함
+증정 용기 이용 간편 조리 — 전자레인지 전용 용기가 함께 증정되어 조리가 편리함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 간단한 조리 — 닭가슴살이 촉촉하며 전자레인지로 데워 먹기 편리함
-다양하고 맛있는 양념 — 떡볶이맛 등 맛있는 양념이 어우러져 질리지 않음</t>
+          <t>촉촉한 식감과 맛있는 양념 — 퍽퍽하지 않고 촉촉하며 떡볶이 맛 등 양념 맛이 우수함
+전자레인지 간편 조리 — 전자레인지에 데워 바로 먹을 수 있어 식사 대용으로 간편함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 상품 구성 — 닭가슴살 외에도 다양한 상품이 포함되어 질리지 않음
-전용 렌지 용기 증정 — 전자레인지용 전용 용기가 함께 제공되어 간편히 데움
-부드럽고 촉촉한 질감 — 퍽퍽함 없이 촉촉하여 부담 없이 먹기 좋음</t>
+          <t>껍질 안 까는 흰자 간편식 — 계란 껍질을 깔 필요 없이 흰자만 깔끔하게 단백질 보충 가능함
+비리지 않고 적절한 간 — 비린 맛이 없고 적당히 짭짤하여 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>계란 흰자만 간편 섭취 — 삶거나 껍질을 깔 필요 없이 흰자만 바로 먹기 유용함
-비린 맛없는 적당한 간 — 비린내가 나지 않고 적당히 짭짤하여 아침 대용으로 적합함
-노른자 없이 낮은 칼로리 — 노른자가 빠져 퍽퍽하지 않고 칼로리 부담 없이 단백질 채움</t>
+          <t>비린 맛 없는 음료 같은 맛 — 단백질 음료 특유의 비린 맛이나 느끼함 없이 음료처럼 마시기 좋음
+운동 후 간편 단백질 보충 — 운동 후 챙겨 먹기 편하며 배고픔을 달래주는 포만감이 있음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛없는 맛있는 풍미 — 프로틴 특유의 비린 맛이 없고 음료처럼 달콤하고 맛있음
-운동 후 든든한 포만감 — 운동 후 섭취 시 배고픔이 줄고 포만감이 오래 유지됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>부드러운 육질과 다양성 — 닭가슴살 육질이 부드럽고 다채로운 맛이 포함되어 만족스러움
+다이어트 간편 식단 — 조리가 간편하여 지속적인 다이어트 체중 관리 식단으로 이용하기 좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>과한 단맛에 대한 아쉬움 — 단맛이 다소 강하여 조금 덜 달았으면 하는 아쉬움이 있음
-이전 대비 줄어든 용량 — 기존 제품에 비해 2g 용량으로 양이 적게 느껴짐</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>오간자 포장 누락 배송 — 선물용 오간자 포장이 누락되어 배송되는 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>과한 단맛과 변경된 용량 — 단맛이 세게 느껴질 수 있으며 기존 대비 용량과 맛에 변화가 있음</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 안내 부족 — 이벤트 기프티콘 확인 방법에 대한 설명이 불명확함</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>포토카드 누락 및 구겨짐 — 배송 시 포토카드가 구겨져 올 위험이 있어 포장 주의가 요구됨</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>오간자 포장 누락 배송 — 안내와 달리 오간자 포장이 빠진 상태로 배송되는 경우 발생함</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>배송 박스 상태 아쉬움 — 제품은 양호하나 배송용 박스가 깨끗하지 않고 재활용 느낌이 남</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>단일 맛 구성과 박스 상태 — 혼합 맛 구성 옵션이 없으며 배송 박스 위생 상태가 아쉬움</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4204,52 +3923,52 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>44,500원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>64,200원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>39,000원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>112,200원</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>44,500원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>64,200원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>39,000원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
         </is>
       </c>
     </row>
@@ -4878,638 +4597,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>1위</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2위</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>3위</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>4위</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>5위</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>6위</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>7위</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>8위</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>9위</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>10위</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="100" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>썸네일</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대원제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] 덴프스 트루바이타민 맥스 5종 택1</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>평점</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>리뷰수</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
-        <v>661</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="n">
-        <v>26201</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>긍정리뷰</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>부정리뷰</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>9,800원</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>13,500원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>22,700원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>18,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A11"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>비율(%)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>카카오선물하기</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>